--- a/outputs/daily/hr_rankings_2026-10-11_remaining.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-11_remaining.xlsx
@@ -760,12 +760,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>54.8</v>
+        <v>57.6</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -808,10 +808,10 @@
         <v>18.6</v>
       </c>
       <c r="R2" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S2" t="n">
-        <v>88.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T2" t="n">
         <v>80</v>
@@ -821,39 +821,35 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -996,8 +992,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="BI2" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -1036,7 +1040,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1060,7 +1064,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>49.7</v>
+        <v>52.2</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1074,7 +1078,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -1084,10 +1088,10 @@
         <v>26.6</v>
       </c>
       <c r="R3" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S3" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T3" t="n">
         <v>78</v>
@@ -1097,39 +1101,35 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1272,8 +1272,16 @@
           <t>25.27</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="BI3" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -1287,24 +1295,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>669257</t>
+          <t>641343</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Will Smith</t>
+          <t>Jake Bauers</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>2026-10-12T00:00:00Z</t>
@@ -1312,7 +1320,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1322,21 +1330,21 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Jacob Misiorowski</t>
+          <t>Tarik Skubal</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>694819</t>
+          <t>669373</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>47.6</v>
+        <v>50.7</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1350,62 +1358,58 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>51.1</v>
+        <v>59.6</v>
       </c>
       <c r="Q4" t="n">
-        <v>18.6</v>
+        <v>26.6</v>
       </c>
       <c r="R4" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S4" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T4" t="n">
         <v>50</v>
       </c>
       <c r="U4" t="n">
-        <v>100</v>
+        <v>16.6</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1425,131 +1429,139 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Last 7 games: 6/26, 0 HR</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>12.34</t>
+          <t>13.91</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>42.97</t>
+          <t>50.01</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>89.76</t>
+          <t>91.98</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>100.2559</t>
+          <t>102.9654</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.5002</t>
+          <t>0.464</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.2249</t>
+          <t>0.2167</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.3857</t>
+          <t>0.3659</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>69.77</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>69.02</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>30.74</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.1765</t>
+          <t>0.2018</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>7.12</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>34.26</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>87.74</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>0.2817</t>
+          <t>0.3398</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0.0996</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>25.57</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
+          <t>25.27</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="BI4" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -1563,24 +1575,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>641343</t>
+          <t>669257</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jake Bauers</t>
+          <t>Will Smith</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>2026-10-12T00:00:00Z</t>
@@ -1588,31 +1600,31 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Tarik Skubal</t>
+          <t>Jacob Misiorowski</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>669373</t>
+          <t>694819</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>47</v>
+        <v>50.4</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1626,62 +1638,58 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>59.6</v>
+        <v>51.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>26.6</v>
+        <v>18.6</v>
       </c>
       <c r="R5" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S5" t="n">
-        <v>81.90000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T5" t="n">
         <v>50</v>
       </c>
       <c r="U5" t="n">
-        <v>16.6</v>
+        <v>100</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1701,131 +1709,139 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 0 HR</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 15.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>13.91</t>
+          <t>12.34</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>50.01</t>
+          <t>42.97</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>91.98</t>
+          <t>89.76</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>102.9654</t>
+          <t>100.2559</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.464</t>
+          <t>0.5002</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.2167</t>
+          <t>0.2249</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.3659</t>
+          <t>0.3857</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>69.77</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>69.02</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>30.74</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.2018</t>
+          <t>0.1765</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>34.26</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>87.74</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.3398</t>
+          <t>0.2817</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.0996</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>25.27</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
+          <t>25.57</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="BI5" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -1864,7 +1880,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1888,7 +1904,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>45.4</v>
+        <v>47.9</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1902,7 +1918,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -1912,10 +1928,10 @@
         <v>26.6</v>
       </c>
       <c r="R6" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S6" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T6" t="n">
         <v>78</v>
@@ -1925,39 +1941,35 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2100,8 +2112,16 @@
           <t>25.27</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="BI6" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -2115,24 +2135,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>596142</t>
+          <t>571970</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Gary Sanchez</t>
+          <t>Max Muncy</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>2026-10-12T00:00:00Z</t>
@@ -2140,31 +2160,31 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Tarik Skubal</t>
+          <t>Jacob Misiorowski</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>669373</t>
+          <t>694819</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>44.3</v>
+        <v>47.4</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2178,62 +2198,58 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>38.4</v>
+        <v>55.1</v>
       </c>
       <c r="Q7" t="n">
-        <v>26.6</v>
+        <v>18.6</v>
       </c>
       <c r="R7" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S7" t="n">
-        <v>90.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T7" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U7" t="n">
-        <v>28.9</v>
+        <v>18</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2253,131 +2269,139 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 1 HR</t>
+          <t>Last 7 games: 6/25, 0 HR</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.1% barrel, 15.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>9.15</t>
+          <t>13.11</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>42.05</t>
+          <t>47.51</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>89.52</t>
+          <t>90.32</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>100.6173</t>
+          <t>101.2892</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.4042</t>
+          <t>0.4781</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1782</t>
+          <t>0.2366</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3297</t>
+          <t>0.3565</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>71.85</t>
+          <t>71.24</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>25.54</t>
+          <t>14.06</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>46.82</t>
+          <t>51.36</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>27.65</t>
+          <t>35.16</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>9.9</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.2052</t>
+          <t>0.2347</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>34.26</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>87.74</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>0.3398</t>
+          <t>0.2817</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.0996</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>25.27</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+          <t>25.57</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -2416,7 +2440,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2440,7 +2464,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>43.7</v>
+        <v>46.3</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2454,7 +2478,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -2464,10 +2488,10 @@
         <v>26.6</v>
       </c>
       <c r="R8" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S8" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T8" t="n">
         <v>50</v>
@@ -2477,39 +2501,35 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2652,8 +2672,16 @@
           <t>25.27</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="BI8" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -2692,12 +2720,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -2716,7 +2744,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>42.3</v>
+        <v>45.3</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2730,7 +2758,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -2740,10 +2768,10 @@
         <v>18.6</v>
       </c>
       <c r="R9" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S9" t="n">
-        <v>92.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="T9" t="n">
         <v>80</v>
@@ -2753,39 +2781,35 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2928,8 +2952,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="BI9" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -2948,7 +2980,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Teoscar Hernandez</t>
+          <t>Teoscar Hernández</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2968,12 +3000,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -2992,7 +3024,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>39</v>
+        <v>44.6</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3006,7 +3038,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -3016,10 +3048,10 @@
         <v>18.6</v>
       </c>
       <c r="R10" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S10" t="n">
-        <v>59.8</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T10" t="n">
         <v>50</v>
@@ -3029,39 +3061,35 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3204,8 +3232,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="BI10" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -3219,24 +3255,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>605141</t>
+          <t>669003</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Mookie Betts</t>
+          <t>Garrett Mitchell</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>2026-10-12T00:00:00Z</t>
@@ -3244,31 +3280,31 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Jacob Misiorowski</t>
+          <t>Tarik Skubal</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>694819</t>
+          <t>669373</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>38.7</v>
+        <v>43.8</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3282,62 +3318,58 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>32.7</v>
+        <v>47.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>18.6</v>
+        <v>26.6</v>
       </c>
       <c r="R11" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S11" t="n">
-        <v>95.5</v>
+        <v>76.2</v>
       </c>
       <c r="T11" t="n">
         <v>50</v>
       </c>
       <c r="U11" t="n">
-        <v>29.2</v>
+        <v>13.3</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3362,126 +3394,134 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/26, 1 HR</t>
+          <t>Last 7 games: 5/24, 0 HR</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>37.34</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>89.87</t>
+          <t>92.36</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>98.5265</t>
+          <t>103.8477</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.4311</t>
+          <t>0.4152</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.1567</t>
+          <t>0.1589</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3363</t>
+          <t>0.3335</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>69.46</t>
+          <t>77.15</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>77.51</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>32.81</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>33.31</t>
+          <t>16.78</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.1823</t>
+          <t>0.1342</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>7.12</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>34.26</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>87.74</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>0.2817</t>
+          <t>0.3398</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>0.0996</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>25.57</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
+          <t>25.27</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="BI11" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -3495,12 +3535,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>669003</t>
+          <t>683734</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Garrett Mitchell</t>
+          <t>Andrew Vaughn</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -3520,12 +3560,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -3544,7 +3584,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>37.9</v>
+        <v>43.5</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3558,62 +3598,58 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>47.1</v>
+        <v>34.2</v>
       </c>
       <c r="Q12" t="n">
         <v>26.6</v>
       </c>
       <c r="R12" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S12" t="n">
-        <v>47.9</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U12" t="n">
-        <v>13.3</v>
+        <v>13.6</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3633,12 +3669,12 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -3648,82 +3684,82 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/24, 0 HR</t>
+          <t>Last 7 games: 4/19, 0 HR</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 15.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>44.76</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>92.36</t>
+          <t>90.55</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>103.8477</t>
+          <t>100.1817</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.4152</t>
+          <t>0.4097</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.1589</t>
+          <t>0.143</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3335</t>
+          <t>0.335</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>77.15</t>
+          <t>70.53</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>77.51</t>
+          <t>12.73</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>32.81</t>
+          <t>33.72</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>16.78</t>
+          <t>24.97</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.1342</t>
+          <t>0.1437</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
@@ -3756,8 +3792,16 @@
           <t>25.27</t>
         </is>
       </c>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -3771,12 +3815,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>663656</t>
+          <t>605141</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Kyle Tucker</t>
+          <t>Mookie Betts</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -3796,12 +3840,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -3820,7 +3864,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>37.6</v>
+        <v>40.3</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3834,62 +3878,58 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>33.9</v>
+        <v>32.7</v>
       </c>
       <c r="Q13" t="n">
         <v>18.6</v>
       </c>
       <c r="R13" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S13" t="n">
-        <v>71.7</v>
+        <v>93.2</v>
       </c>
       <c r="T13" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U13" t="n">
-        <v>12</v>
+        <v>29.2</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3914,22 +3954,22 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Last 7 games: 5/26, 1 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -3939,67 +3979,67 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>7.11</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>37.53</t>
+          <t>37.34</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>88.98</t>
+          <t>89.87</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>98.7109</t>
+          <t>98.5265</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.4311</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.1598</t>
+          <t>0.1567</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3433</t>
+          <t>0.3363</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>71.58</t>
+          <t>69.46</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>20.59</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>42.96</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>33.31</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.1658</t>
+          <t>0.1823</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
@@ -4032,8 +4072,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="BI13" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -4047,12 +4095,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>691777</t>
+          <t>681624</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Max Muncy</t>
+          <t>Andy Pages</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -4072,12 +4120,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -4096,7 +4144,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>37.4</v>
+        <v>39.3</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4110,62 +4158,58 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>35.1</v>
+        <v>36.4</v>
       </c>
       <c r="Q14" t="n">
         <v>18.6</v>
       </c>
       <c r="R14" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S14" t="n">
-        <v>81.90000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="T14" t="n">
         <v>50</v>
       </c>
       <c r="U14" t="n">
-        <v>26.1</v>
+        <v>66</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4185,22 +4229,22 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/17, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
@@ -4215,89 +4259,89 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>10.52</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>40.17</t>
+          <t>40.77</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>88.81</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>100.9708</t>
+          <t>99.6965</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.3621</t>
+          <t>0.4378</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.1493</t>
+          <t>0.1686</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
+          <t>0.3349</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>72.85</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>26.4</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>38.53</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>29.0</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>24.2</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>0.1925</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>34.56</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>87.74</t>
+        </is>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
           <t>0.2817</t>
         </is>
       </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>73.8</t>
-        </is>
-      </c>
-      <c r="AV14" t="inlineStr">
-        <is>
-          <t>42.11</t>
-        </is>
-      </c>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>43.52</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>22.51</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>9.0</t>
-        </is>
-      </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>0.1594</t>
-        </is>
-      </c>
-      <c r="BA14" t="inlineStr">
-        <is>
-          <t>4.89</t>
-        </is>
-      </c>
-      <c r="BB14" t="inlineStr">
-        <is>
-          <t>34.56</t>
-        </is>
-      </c>
-      <c r="BC14" t="inlineStr">
-        <is>
-          <t>87.74</t>
-        </is>
-      </c>
-      <c r="BD14" t="inlineStr">
-        <is>
-          <t>0.2817</t>
-        </is>
-      </c>
       <c r="BE14" t="inlineStr">
         <is>
           <t>0.0996</t>
@@ -4308,8 +4352,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="BI14" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -4323,12 +4375,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>681624</t>
+          <t>663656</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Andy Pages</t>
+          <t>Kyle Tucker</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -4348,7 +4400,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4372,7 +4424,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>35.1</v>
+        <v>36.8</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4386,62 +4438,58 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>36.4</v>
+        <v>33.9</v>
       </c>
       <c r="Q15" t="n">
         <v>18.6</v>
       </c>
       <c r="R15" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S15" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T15" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U15" t="n">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4461,27 +4509,27 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -4491,67 +4539,67 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>40.77</t>
+          <t>37.53</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>88.81</t>
+          <t>88.98</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>99.6965</t>
+          <t>98.7109</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.4378</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.1686</t>
+          <t>0.1598</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3349</t>
+          <t>0.3433</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>72.85</t>
+          <t>71.58</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>20.59</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>38.53</t>
+          <t>42.96</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.1925</t>
+          <t>0.1658</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
@@ -4584,8 +4632,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -4599,24 +4655,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>800325</t>
+          <t>571771</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Luis Lara</t>
+          <t>Enrique Hernández</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-12T00:00:00Z</t>
@@ -4624,31 +4680,31 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Tarik Skubal</t>
+          <t>Jacob Misiorowski</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>669373</t>
+          <t>694819</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>32.7</v>
+        <v>33.4</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4662,65 +4718,61 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>16.6</v>
+        <v>32.6</v>
       </c>
       <c r="Q16" t="n">
-        <v>25</v>
+        <v>18.6</v>
       </c>
       <c r="R16" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S16" t="n">
-        <v>71.7</v>
+        <v>44.8</v>
       </c>
       <c r="T16" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U16" t="n">
-        <v>5.1</v>
+        <v>28.5</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr"/>
@@ -4737,27 +4789,27 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/26, 0 HR</t>
+          <t>Last 7 games: 3/16, 1 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 7.1% barrel, 15.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -4767,101 +4819,109 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>8.52</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>39.49</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>89.39</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>98.8409</t>
+          <t>99.9102</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>0.3751</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>0.1548</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.293</t>
+          <t>0.2814</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>70.82</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>14.8</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>31.9</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>25.54</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>0.1735</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>34.26</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>87.74</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>0.3398</t>
+          <t>0.2817</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.0996</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>25.27</t>
-        </is>
-      </c>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
+          <t>25.57</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="BI16" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -4900,7 +4960,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -4924,7 +4984,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>30.6</v>
+        <v>33.1</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -4938,7 +4998,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -4948,10 +5008,10 @@
         <v>26.6</v>
       </c>
       <c r="R17" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S17" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T17" t="n">
         <v>78</v>
@@ -4961,39 +5021,35 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -5136,8 +5192,16 @@
           <t>25.27</t>
         </is>
       </c>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="BI17" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -5151,24 +5215,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>669242</t>
+          <t>687401</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tommy Edman</t>
+          <t>Joey Ortiz</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>2026-10-12T00:00:00Z</t>
@@ -5176,7 +5240,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -5186,21 +5250,21 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Jacob Misiorowski</t>
+          <t>Tarik Skubal</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>694819</t>
+          <t>669373</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>30.4</v>
+        <v>32.5</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5214,62 +5278,58 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>20.2</v>
+        <v>17.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>17.3</v>
+        <v>26.6</v>
       </c>
       <c r="R18" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S18" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T18" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="U18" t="n">
-        <v>60.7</v>
+        <v>22.4</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5294,22 +5354,22 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 7/26, 0 HR</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -5319,101 +5379,109 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>34.37</t>
+          <t>36.16</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>87.91</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>98.7457</t>
+          <t>99.2209</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.3662</t>
+          <t>0.3403</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>0.0967</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.3084</t>
+          <t>0.2904</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>13.58</t>
+          <t>30.57</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>42.25</t>
+          <t>31.91</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>19.68</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.1437</t>
+          <t>0.1185</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>7.12</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>34.26</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>87.74</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>0.2817</t>
+          <t>0.3398</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>0.0996</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>25.57</t>
-        </is>
-      </c>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
+          <t>25.27</t>
+        </is>
+      </c>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="BI18" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -5427,12 +5495,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>687401</t>
+          <t>800325</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Joey Ortiz</t>
+          <t>Luis Lara</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -5452,12 +5520,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -5476,7 +5544,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>29.9</v>
+        <v>31.8</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5490,65 +5558,61 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>17.1</v>
+        <v>16.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>26.6</v>
+        <v>25</v>
       </c>
       <c r="R19" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>52.4</v>
       </c>
       <c r="T19" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U19" t="n">
-        <v>22.4</v>
+        <v>5.1</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr"/>
@@ -5565,7 +5629,7 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
@@ -5580,12 +5644,12 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/26, 0 HR</t>
+          <t>Last 7 games: 4/26, 0 HR</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.1% barrel, 15.2 HR allowed</t>
+          <t>switch hitter; pitcher baseline 7.1% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -5595,67 +5659,67 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>36.16</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>87.91</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>99.2209</t>
+          <t>98.8409</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.3403</t>
+          <t>0.331</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>0.0967</t>
+          <t>0.075</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.2904</t>
+          <t>0.293</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>30.57</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>31.91</t>
+          <t>30.6</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>19.68</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.1185</t>
+          <t>0.079</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
@@ -5688,8 +5752,16 @@
           <t>25.27</t>
         </is>
       </c>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="BI19" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -6054,12 +6126,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -6078,7 +6150,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>54.8</v>
+        <v>57.6</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -6092,7 +6164,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -6102,10 +6174,10 @@
         <v>18.6</v>
       </c>
       <c r="R2" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S2" t="n">
-        <v>88.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T2" t="n">
         <v>80</v>
@@ -6115,39 +6187,35 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6290,8 +6358,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="BI2" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -6330,7 +6406,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -6354,7 +6430,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>49.7</v>
+        <v>52.2</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -6368,7 +6444,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -6378,10 +6454,10 @@
         <v>26.6</v>
       </c>
       <c r="R3" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S3" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T3" t="n">
         <v>78</v>
@@ -6391,39 +6467,35 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6566,8 +6638,16 @@
           <t>25.27</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="BI3" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -6581,24 +6661,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>669257</t>
+          <t>641343</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Will Smith</t>
+          <t>Jake Bauers</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>2026-10-12T00:00:00Z</t>
@@ -6606,7 +6686,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -6616,21 +6696,21 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Jacob Misiorowski</t>
+          <t>Tarik Skubal</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>694819</t>
+          <t>669373</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>47.6</v>
+        <v>50.7</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -6644,62 +6724,58 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>51.1</v>
+        <v>59.6</v>
       </c>
       <c r="Q4" t="n">
-        <v>18.6</v>
+        <v>26.6</v>
       </c>
       <c r="R4" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S4" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T4" t="n">
         <v>50</v>
       </c>
       <c r="U4" t="n">
-        <v>100</v>
+        <v>16.6</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6719,131 +6795,139 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Last 7 games: 6/26, 0 HR</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>12.34</t>
+          <t>13.91</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>42.97</t>
+          <t>50.01</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>89.76</t>
+          <t>91.98</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>100.2559</t>
+          <t>102.9654</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.5002</t>
+          <t>0.464</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.2249</t>
+          <t>0.2167</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.3857</t>
+          <t>0.3659</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>69.77</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>69.02</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>30.74</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.1765</t>
+          <t>0.2018</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>7.12</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>34.26</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>87.74</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>0.2817</t>
+          <t>0.3398</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0.0996</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>25.57</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
+          <t>25.27</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="BI4" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -6857,24 +6941,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>641343</t>
+          <t>669257</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jake Bauers</t>
+          <t>Will Smith</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>2026-10-12T00:00:00Z</t>
@@ -6882,31 +6966,31 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Tarik Skubal</t>
+          <t>Jacob Misiorowski</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>669373</t>
+          <t>694819</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>47</v>
+        <v>50.4</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -6920,62 +7004,58 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>59.6</v>
+        <v>51.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>26.6</v>
+        <v>18.6</v>
       </c>
       <c r="R5" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S5" t="n">
-        <v>81.90000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T5" t="n">
         <v>50</v>
       </c>
       <c r="U5" t="n">
-        <v>16.6</v>
+        <v>100</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6995,131 +7075,139 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 0 HR</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 15.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>13.91</t>
+          <t>12.34</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>50.01</t>
+          <t>42.97</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>91.98</t>
+          <t>89.76</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>102.9654</t>
+          <t>100.2559</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.464</t>
+          <t>0.5002</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.2167</t>
+          <t>0.2249</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.3659</t>
+          <t>0.3857</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>69.77</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>69.02</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>30.74</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.2018</t>
+          <t>0.1765</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>34.26</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>87.74</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.3398</t>
+          <t>0.2817</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.0996</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>25.27</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
+          <t>25.57</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="BI5" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -7158,7 +7246,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -7182,7 +7270,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>45.4</v>
+        <v>47.9</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7196,7 +7284,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -7206,10 +7294,10 @@
         <v>26.6</v>
       </c>
       <c r="R6" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S6" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T6" t="n">
         <v>78</v>
@@ -7219,39 +7307,35 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7394,8 +7478,16 @@
           <t>25.27</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="BI6" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -7409,24 +7501,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>596142</t>
+          <t>571970</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Gary Sanchez</t>
+          <t>Max Muncy</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>2026-10-12T00:00:00Z</t>
@@ -7434,31 +7526,31 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Tarik Skubal</t>
+          <t>Jacob Misiorowski</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>669373</t>
+          <t>694819</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>44.3</v>
+        <v>47.4</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7472,62 +7564,58 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>38.4</v>
+        <v>55.1</v>
       </c>
       <c r="Q7" t="n">
-        <v>26.6</v>
+        <v>18.6</v>
       </c>
       <c r="R7" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S7" t="n">
-        <v>90.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T7" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U7" t="n">
-        <v>28.9</v>
+        <v>18</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7547,131 +7635,139 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 1 HR</t>
+          <t>Last 7 games: 6/25, 0 HR</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.1% barrel, 15.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>9.15</t>
+          <t>13.11</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>42.05</t>
+          <t>47.51</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>89.52</t>
+          <t>90.32</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>100.6173</t>
+          <t>101.2892</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.4042</t>
+          <t>0.4781</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1782</t>
+          <t>0.2366</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3297</t>
+          <t>0.3565</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>71.85</t>
+          <t>71.24</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>25.54</t>
+          <t>14.06</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>46.82</t>
+          <t>51.36</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>27.65</t>
+          <t>35.16</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>9.9</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.2052</t>
+          <t>0.2347</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>34.26</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>87.74</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>0.3398</t>
+          <t>0.2817</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.0996</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>25.27</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+          <t>25.57</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -7710,7 +7806,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -7734,7 +7830,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>43.7</v>
+        <v>46.3</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7748,7 +7844,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -7758,10 +7854,10 @@
         <v>26.6</v>
       </c>
       <c r="R8" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S8" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T8" t="n">
         <v>50</v>
@@ -7771,39 +7867,35 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7946,8 +8038,16 @@
           <t>25.27</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="BI8" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -7986,12 +8086,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -8010,7 +8110,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>42.3</v>
+        <v>45.3</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8024,7 +8124,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -8034,10 +8134,10 @@
         <v>18.6</v>
       </c>
       <c r="R9" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S9" t="n">
-        <v>92.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="T9" t="n">
         <v>80</v>
@@ -8047,39 +8147,35 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8222,8 +8318,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="BI9" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -8242,7 +8346,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Teoscar Hernandez</t>
+          <t>Teoscar Hernández</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -8262,12 +8366,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -8286,7 +8390,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>39</v>
+        <v>44.6</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8300,7 +8404,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -8310,10 +8414,10 @@
         <v>18.6</v>
       </c>
       <c r="R10" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S10" t="n">
-        <v>59.8</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T10" t="n">
         <v>50</v>
@@ -8323,39 +8427,35 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8498,8 +8598,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="BI10" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -8513,24 +8621,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>605141</t>
+          <t>669003</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Mookie Betts</t>
+          <t>Garrett Mitchell</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>2026-10-12T00:00:00Z</t>
@@ -8538,31 +8646,31 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Jacob Misiorowski</t>
+          <t>Tarik Skubal</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>694819</t>
+          <t>669373</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>38.7</v>
+        <v>43.8</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -8576,62 +8684,58 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>32.7</v>
+        <v>47.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>18.6</v>
+        <v>26.6</v>
       </c>
       <c r="R11" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S11" t="n">
-        <v>95.5</v>
+        <v>76.2</v>
       </c>
       <c r="T11" t="n">
         <v>50</v>
       </c>
       <c r="U11" t="n">
-        <v>29.2</v>
+        <v>13.3</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8656,126 +8760,134 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/26, 1 HR</t>
+          <t>Last 7 games: 5/24, 0 HR</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>37.34</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>89.87</t>
+          <t>92.36</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>98.5265</t>
+          <t>103.8477</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.4311</t>
+          <t>0.4152</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.1567</t>
+          <t>0.1589</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3363</t>
+          <t>0.3335</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>69.46</t>
+          <t>77.15</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>77.51</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>32.81</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>33.31</t>
+          <t>16.78</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.1823</t>
+          <t>0.1342</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>7.12</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>34.26</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>87.74</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>0.2817</t>
+          <t>0.3398</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>0.0996</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>25.57</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
+          <t>25.27</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="BI11" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -8789,12 +8901,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>669003</t>
+          <t>683734</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Garrett Mitchell</t>
+          <t>Andrew Vaughn</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -8814,12 +8926,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -8838,7 +8950,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>37.9</v>
+        <v>43.5</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -8852,62 +8964,58 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>47.1</v>
+        <v>34.2</v>
       </c>
       <c r="Q12" t="n">
         <v>26.6</v>
       </c>
       <c r="R12" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S12" t="n">
-        <v>47.9</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U12" t="n">
-        <v>13.3</v>
+        <v>13.6</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8927,12 +9035,12 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -8942,82 +9050,82 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/24, 0 HR</t>
+          <t>Last 7 games: 4/19, 0 HR</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 15.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>44.76</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>92.36</t>
+          <t>90.55</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>103.8477</t>
+          <t>100.1817</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.4152</t>
+          <t>0.4097</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.1589</t>
+          <t>0.143</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3335</t>
+          <t>0.335</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>77.15</t>
+          <t>70.53</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>77.51</t>
+          <t>12.73</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>32.81</t>
+          <t>33.72</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>16.78</t>
+          <t>24.97</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.1342</t>
+          <t>0.1437</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
@@ -9050,8 +9158,16 @@
           <t>25.27</t>
         </is>
       </c>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -9065,12 +9181,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>663656</t>
+          <t>605141</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Kyle Tucker</t>
+          <t>Mookie Betts</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -9090,12 +9206,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -9114,7 +9230,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>37.6</v>
+        <v>40.3</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9128,62 +9244,58 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>33.9</v>
+        <v>32.7</v>
       </c>
       <c r="Q13" t="n">
         <v>18.6</v>
       </c>
       <c r="R13" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S13" t="n">
-        <v>71.7</v>
+        <v>93.2</v>
       </c>
       <c r="T13" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U13" t="n">
-        <v>12</v>
+        <v>29.2</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9208,22 +9320,22 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Last 7 games: 5/26, 1 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -9233,67 +9345,67 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>7.11</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>37.53</t>
+          <t>37.34</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>88.98</t>
+          <t>89.87</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>98.7109</t>
+          <t>98.5265</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.4311</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.1598</t>
+          <t>0.1567</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3433</t>
+          <t>0.3363</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>71.58</t>
+          <t>69.46</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>20.59</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>42.96</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>33.31</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.1658</t>
+          <t>0.1823</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
@@ -9326,8 +9438,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="BI13" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -9341,12 +9461,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>691777</t>
+          <t>681624</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Max Muncy</t>
+          <t>Andy Pages</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -9366,12 +9486,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -9390,7 +9510,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>37.4</v>
+        <v>39.3</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -9404,62 +9524,58 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>35.1</v>
+        <v>36.4</v>
       </c>
       <c r="Q14" t="n">
         <v>18.6</v>
       </c>
       <c r="R14" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S14" t="n">
-        <v>81.90000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="T14" t="n">
         <v>50</v>
       </c>
       <c r="U14" t="n">
-        <v>26.1</v>
+        <v>66</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9479,22 +9595,22 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/17, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
@@ -9509,89 +9625,89 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>10.52</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>40.17</t>
+          <t>40.77</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>88.81</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>100.9708</t>
+          <t>99.6965</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.3621</t>
+          <t>0.4378</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.1493</t>
+          <t>0.1686</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
+          <t>0.3349</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>72.85</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>26.4</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>38.53</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>29.0</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>24.2</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>0.1925</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>34.56</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>87.74</t>
+        </is>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
           <t>0.2817</t>
         </is>
       </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>73.8</t>
-        </is>
-      </c>
-      <c r="AV14" t="inlineStr">
-        <is>
-          <t>42.11</t>
-        </is>
-      </c>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>43.52</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>22.51</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>9.0</t>
-        </is>
-      </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>0.1594</t>
-        </is>
-      </c>
-      <c r="BA14" t="inlineStr">
-        <is>
-          <t>4.89</t>
-        </is>
-      </c>
-      <c r="BB14" t="inlineStr">
-        <is>
-          <t>34.56</t>
-        </is>
-      </c>
-      <c r="BC14" t="inlineStr">
-        <is>
-          <t>87.74</t>
-        </is>
-      </c>
-      <c r="BD14" t="inlineStr">
-        <is>
-          <t>0.2817</t>
-        </is>
-      </c>
       <c r="BE14" t="inlineStr">
         <is>
           <t>0.0996</t>
@@ -9602,8 +9718,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="BI14" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -9617,12 +9741,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>681624</t>
+          <t>663656</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Andy Pages</t>
+          <t>Kyle Tucker</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -9642,7 +9766,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -9666,7 +9790,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>35.1</v>
+        <v>36.8</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9680,62 +9804,58 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>36.4</v>
+        <v>33.9</v>
       </c>
       <c r="Q15" t="n">
         <v>18.6</v>
       </c>
       <c r="R15" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S15" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T15" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U15" t="n">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9755,27 +9875,27 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -9785,67 +9905,67 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>40.77</t>
+          <t>37.53</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>88.81</t>
+          <t>88.98</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>99.6965</t>
+          <t>98.7109</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.4378</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.1686</t>
+          <t>0.1598</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3349</t>
+          <t>0.3433</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>72.85</t>
+          <t>71.58</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>20.59</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>38.53</t>
+          <t>42.96</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.1925</t>
+          <t>0.1658</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
@@ -9878,8 +9998,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -9893,24 +10021,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>800325</t>
+          <t>571771</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Luis Lara</t>
+          <t>Enrique Hernández</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-12T00:00:00Z</t>
@@ -9918,31 +10046,31 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Tarik Skubal</t>
+          <t>Jacob Misiorowski</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>669373</t>
+          <t>694819</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>32.7</v>
+        <v>33.4</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -9956,65 +10084,61 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>16.6</v>
+        <v>32.6</v>
       </c>
       <c r="Q16" t="n">
-        <v>25</v>
+        <v>18.6</v>
       </c>
       <c r="R16" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S16" t="n">
-        <v>71.7</v>
+        <v>44.8</v>
       </c>
       <c r="T16" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U16" t="n">
-        <v>5.1</v>
+        <v>28.5</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr"/>
@@ -10031,27 +10155,27 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/26, 0 HR</t>
+          <t>Last 7 games: 3/16, 1 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 7.1% barrel, 15.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -10061,101 +10185,109 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>8.52</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>39.49</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>89.39</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>98.8409</t>
+          <t>99.9102</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>0.3751</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>0.1548</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.293</t>
+          <t>0.2814</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>70.82</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>14.8</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>31.9</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>25.54</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>0.1735</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>34.26</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>87.74</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>0.3398</t>
+          <t>0.2817</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.0996</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>25.27</t>
-        </is>
-      </c>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
+          <t>25.57</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="BI16" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -10194,7 +10326,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -10218,7 +10350,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>30.6</v>
+        <v>33.1</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -10232,7 +10364,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -10242,10 +10374,10 @@
         <v>26.6</v>
       </c>
       <c r="R17" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S17" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T17" t="n">
         <v>78</v>
@@ -10255,39 +10387,35 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -10430,8 +10558,16 @@
           <t>25.27</t>
         </is>
       </c>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="BI17" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -10445,24 +10581,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>669242</t>
+          <t>687401</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tommy Edman</t>
+          <t>Joey Ortiz</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>2026-10-12T00:00:00Z</t>
@@ -10470,7 +10606,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -10480,21 +10616,21 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Jacob Misiorowski</t>
+          <t>Tarik Skubal</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>694819</t>
+          <t>669373</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>30.4</v>
+        <v>32.5</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -10508,62 +10644,58 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>20.2</v>
+        <v>17.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>17.3</v>
+        <v>26.6</v>
       </c>
       <c r="R18" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S18" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T18" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="U18" t="n">
-        <v>60.7</v>
+        <v>22.4</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10588,22 +10720,22 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 7/26, 0 HR</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -10613,101 +10745,109 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>34.37</t>
+          <t>36.16</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>87.91</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>98.7457</t>
+          <t>99.2209</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.3662</t>
+          <t>0.3403</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>0.0967</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.3084</t>
+          <t>0.2904</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>13.58</t>
+          <t>30.57</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>42.25</t>
+          <t>31.91</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>19.68</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.1437</t>
+          <t>0.1185</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>7.12</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>34.26</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>87.74</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>0.2817</t>
+          <t>0.3398</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>0.0996</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>25.57</t>
-        </is>
-      </c>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
+          <t>25.27</t>
+        </is>
+      </c>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="BI18" t="inlineStr">
         <is>
           <t>American Family Field</t>
@@ -10721,12 +10861,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>687401</t>
+          <t>800325</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Joey Ortiz</t>
+          <t>Luis Lara</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -10746,12 +10886,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -10770,7 +10910,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>29.9</v>
+        <v>31.8</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -10784,65 +10924,61 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>17.1</v>
+        <v>16.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>26.6</v>
+        <v>25</v>
       </c>
       <c r="R19" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>52.4</v>
       </c>
       <c r="T19" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U19" t="n">
-        <v>22.4</v>
+        <v>5.1</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr"/>
@@ -10859,7 +10995,7 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
@@ -10874,12 +11010,12 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/26, 0 HR</t>
+          <t>Last 7 games: 4/26, 0 HR</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.1% barrel, 15.2 HR allowed</t>
+          <t>switch hitter; pitcher baseline 7.1% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -10889,67 +11025,67 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>36.16</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>87.91</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>99.2209</t>
+          <t>98.8409</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.3403</t>
+          <t>0.331</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>0.0967</t>
+          <t>0.075</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.2904</t>
+          <t>0.293</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>30.57</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>31.91</t>
+          <t>30.6</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>19.68</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.1185</t>
+          <t>0.079</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
@@ -10982,8 +11118,16 @@
           <t>25.27</t>
         </is>
       </c>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
       <c r="BI19" t="inlineStr">
         <is>
           <t>American Family Field</t>
